--- a/Output/Models/List_models_exposure_malf.xlsx
+++ b/Output/Models/List_models_exposure_malf.xlsx
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13041,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17037,7 +17037,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17148,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17185,7 +17185,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17592,7 +17592,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -17999,7 +17999,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18406,7 +18406,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18517,7 +18517,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18554,7 +18554,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18813,7 +18813,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19220,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19331,7 +19331,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19960,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22624,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22735,7 +22735,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22883,7 +22883,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22920,7 +22920,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22957,7 +22957,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23105,7 +23105,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23142,7 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23253,7 +23253,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23290,7 +23290,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23364,7 +23364,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23512,7 +23512,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23549,7 +23549,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23586,7 +23586,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23845,7 +23845,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23956,7 +23956,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24067,7 +24067,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24141,7 +24141,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24178,7 +24178,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24215,7 +24215,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24252,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24363,7 +24363,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24400,7 +24400,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24511,7 +24511,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24548,7 +24548,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24622,7 +24622,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24696,7 +24696,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24733,7 +24733,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24770,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24807,7 +24807,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -24955,7 +24955,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -24992,7 +24992,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25066,7 +25066,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25140,7 +25140,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25214,7 +25214,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25251,7 +25251,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25325,7 +25325,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25362,7 +25362,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25436,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25547,7 +25547,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25621,7 +25621,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25658,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -25954,7 +25954,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26028,7 +26028,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26065,7 +26065,7 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26139,7 +26139,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26250,7 +26250,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -26324,7 +26324,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26361,7 +26361,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26398,7 +26398,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26620,7 +26620,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26805,7 +26805,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26879,7 +26879,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26916,7 +26916,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26953,7 +26953,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -26990,7 +26990,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27508,7 +27508,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27582,7 +27582,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27619,7 +27619,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27656,7 +27656,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27693,7 +27693,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27730,7 +27730,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27767,7 +27767,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -27952,7 +27952,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -27989,7 +27989,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -28063,7 +28063,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28544,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28581,7 +28581,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28655,7 +28655,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28692,7 +28692,7 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28729,7 +28729,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28803,7 +28803,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28840,7 +28840,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -28951,7 +28951,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29062,7 +29062,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29136,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29210,7 +29210,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29691,7 +29691,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29728,7 +29728,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29765,7 +29765,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29802,7 +29802,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29950,7 +29950,7 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -29987,7 +29987,7 @@
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -30024,7 +30024,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30061,7 +30061,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30098,7 +30098,7 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30172,7 +30172,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30209,7 +30209,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30246,7 +30246,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30283,7 +30283,7 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30320,7 +30320,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30357,7 +30357,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30838,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30912,7 +30912,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30949,7 +30949,7 @@
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -31060,7 +31060,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -31097,7 +31097,7 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31134,7 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31171,7 +31171,7 @@
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31208,7 +31208,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31245,7 +31245,7 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31282,7 +31282,7 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31356,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -31911,7 +31911,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -31948,7 +31948,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32022,7 +32022,7 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32207,7 +32207,7 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -32244,7 +32244,7 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32281,7 +32281,7 @@
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32318,7 +32318,7 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32355,7 +32355,7 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32392,7 +32392,7 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32429,7 +32429,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32503,7 +32503,7 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32540,7 +32540,7 @@
       </c>
       <c r="G870" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33021,7 +33021,7 @@
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33058,7 +33058,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33095,7 @@
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33169,7 +33169,7 @@
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33243,7 +33243,7 @@
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33280,7 +33280,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33317,7 +33317,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33391,7 +33391,7 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33428,7 +33428,7 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33576,7 +33576,7 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33613,7 +33613,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -33687,7 +33687,7 @@
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -34094,7 +34094,7 @@
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34131,7 +34131,7 @@
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34168,7 +34168,7 @@
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34242,7 +34242,7 @@
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34353,7 +34353,7 @@
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34390,7 +34390,7 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34427,7 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34501,7 +34501,7 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34612,7 +34612,7 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34686,7 +34686,7 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34723,7 +34723,7 @@
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34760,7 +34760,7 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -34797,7 +34797,7 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -35204,7 +35204,7 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35241,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35278,7 +35278,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35315,7 +35315,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35352,7 +35352,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35389,7 +35389,7 @@
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35426,7 +35426,7 @@
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35500,7 +35500,7 @@
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35537,7 +35537,7 @@
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35611,7 +35611,7 @@
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35648,7 +35648,7 @@
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35685,7 +35685,7 @@
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35722,7 +35722,7 @@
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35759,7 +35759,7 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35796,7 +35796,7 @@
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35833,7 +35833,7 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35870,7 +35870,7 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -35907,7 +35907,7 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
